--- a/セリフ編集/その他セリフ/12-選手経歴イベント.xlsx
+++ b/セリフ編集/その他セリフ/12-選手経歴イベント.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I319"/>
+  <dimension ref="A1:I419"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -10339,8 +10339,3073 @@
         </is>
       </c>
     </row>
+    <row r="320" ht="40" customHeight="1">
+      <c r="A320" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.fresh.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は体が軽い。なんでもできそうな気がする</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="40" customHeight="1">
+      <c r="A321" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.fresh.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">体が動きたがってる。もっとやらせてくれない?</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="40" customHeight="1">
+      <c r="A322" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.fresh.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">なんか今日、体が軽いんだよねー。いけるいける</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="40" customHeight="1">
+      <c r="A323" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.fresh.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">体が素直に動きます。やった分だけ返ってきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="40" customHeight="1">
+      <c r="A324" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.fresh.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">体が軽い…!今ならなんでもできる気がする…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="40" customHeight="1">
+      <c r="A325" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.fresh.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…体が、軽いです。…今日は、いけます</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="40" customHeight="1">
+      <c r="A326" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.fresh.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">な、なんだか今日、体が軽くて…!やれそうです…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="40" customHeight="1">
+      <c r="A327" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">同じだけやってるのに、手応えが薄い気がする</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="40" customHeight="1">
+      <c r="A328" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まだやれる。…切れが鈍った? 気のせいだって</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="40" customHeight="1">
+      <c r="A329" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">んー、なんか乗り切らないなー。動けてはいるけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="40" customHeight="1">
+      <c r="A330" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">同じだけやってるのに、身についてる感じがしません</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="40" customHeight="1">
+      <c r="A331" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あれ…なんか入ってこない…!?もっとやれるはずなのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="40" customHeight="1">
+      <c r="A332" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…同じことを、しているのに。…返るものが、少ない</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="40" customHeight="1">
+      <c r="A333" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.warm.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの…同じようにやってるはずなんですけど…なんだか…</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="40" customHeight="1">
+      <c r="A334" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">体が重い。動いてはいるけど、何も残らないな</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="40" customHeight="1">
+      <c r="A335" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">重い。…でも止まらない。止まったら負けた気がする</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="40" customHeight="1">
+      <c r="A336" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あー、体が重い。今日は何やっても身にならないねー</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="40" customHeight="1">
+      <c r="A337" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">動きが同じところで止まる。私の集中が足りないのかな</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="40" customHeight="1">
+      <c r="A338" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">体が重い…!やる気はあるのに、体がついてこない…!</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="40" customHeight="1">
+      <c r="A339" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…体が、重いです。…今日は、たぶん、残りません</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="40" customHeight="1">
+      <c r="A340" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatSelf.heavy.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、あの…体が重いです…今日は、身になってない気がして…</t>
+        </is>
+      </c>
+    </row>
+    <row r="341" ht="40" customHeight="1">
+      <c r="A341" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[1]</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.fresh[1]</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、今日はよく動いてる。仕込むなら今だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="40" customHeight="1">
+      <c r="A342" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[2]</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.fresh[2]</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}の体が、新しい動きを素直に飲み込んでいる</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="40" customHeight="1">
+      <c r="A343" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[3]</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.fresh[3]</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今の{name}なら、多少きつくしても全部持っていく</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="40" customHeight="1">
+      <c r="A344" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[4]</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.fresh[4]</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}の足が軽い。こういう週こそ厚く積ませたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="40" customHeight="1">
+      <c r="A345" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[5]</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.fresh[5]</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、伸びる顔をしている。今日の一本は残るぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="40" customHeight="1">
+      <c r="A346" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[6]</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.fresh[6]</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}は休み明けの体だ。一番よく入る時期に来ている</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="40" customHeight="1">
+      <c r="A347" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.fresh[7]</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.fresh[7]</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、今週は当たり週だ。使うなら、ここで使え</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="40" customHeight="1">
+      <c r="A348" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[1]</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.warm[1]</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、悪くはない。ただ、先週ほどは入っていかない</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="40" customHeight="1">
+      <c r="A349" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[2]</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.warm[2]</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}の伸びが少し鈍ってきた。詰めすぎたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="40" customHeight="1">
+      <c r="A350" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[3]</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.warm[3]</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、同じメニューなのに返りが薄い。そろそろ一息か</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="40" customHeight="1">
+      <c r="A351" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[4]</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.warm[4]</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、動けてはいる。だが、切れがひとつ落ちている</t>
+        </is>
+      </c>
+    </row>
+    <row r="352" ht="40" customHeight="1">
+      <c r="A352" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[5]</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.warm[5]</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}の体が慣れてきた。効きが落ちる頃合いだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="40" customHeight="1">
+      <c r="A353" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[6]</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.warm[6]</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、今週も同じ調子で行くなら、得は薄いぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="40" customHeight="1">
+      <c r="A354" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.warm[7]</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.warm[7]</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}にきついのを続けるか。…見極めどきだな</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="40" customHeight="1">
+      <c r="A355" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[1]</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.heavy[1]</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、今日は体が重い。何をやらせても素通りだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="40" customHeight="1">
+      <c r="A356" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[2]</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.heavy[2]</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今の{name}に課しても、削るだけで何も積まれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="40" customHeight="1">
+      <c r="A357" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[3]</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.heavy[3]</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}は追い込みすぎだ。一度、外してやってくれ</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="40" customHeight="1">
+      <c r="A358" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[4]</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.heavy[4]</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、汗はかいている。だが、身についてはいない</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="40" customHeight="1">
+      <c r="A359" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[5]</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.heavy[5]</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}の体はもう受け付けていない。休ませれば戻る</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="40" customHeight="1">
+      <c r="A360" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[6]</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.heavy[6]</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今の{name}にやらせるのは、怪我を買うようなものだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="40" customHeight="1">
+      <c r="A361" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatCoach.heavy[7]</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">heatCoach.heavy[7]</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{name}、一週抜けばまた入るようになる。それだけの話だ</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="40" customHeight="1">
+      <c r="A362" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくれた目を信じて、頑張ってみるね</t>
+        </is>
+      </c>
+    </row>
+    <row r="363" ht="40" customHeight="1">
+      <c r="A363" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まさか自分に声がかかるとはね。よろしく</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="40" customHeight="1">
+      <c r="A364" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">期待されてるうちに、いいとこ見せないとね</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="40" customHeight="1">
+      <c r="A365" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見る目あるじゃん。すぐ活躍してみせるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="40" customHeight="1">
+      <c r="A366" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">買われた実力、値段以上だったって言わせてみせるよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="40" customHeight="1">
+      <c r="A367" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…見ていてくれた人が、いたんですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="40" customHeight="1">
+      <c r="A368" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…がんばります。…それだけ、です</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="40" customHeight="1">
+      <c r="A369" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、わたしなんかに声をかけてくれて…！が、頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="40" customHeight="1">
+      <c r="A370" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">き、期待外れって言われないように…します…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="40" customHeight="1">
+      <c r="A371" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よく見つけたねー。掘り出し物だよ、あたし</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="40" customHeight="1">
+      <c r="A372" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ちょうど暴れる場所探してたんだ。よろしくね</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="40" customHeight="1">
+      <c r="A373" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見ていてくれた人がいた。それだけで頑張れます</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="40" customHeight="1">
+      <c r="A374" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">期待してもらった分、毎日積み上げていきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="40" customHeight="1">
+      <c r="A375" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてもらえた…！嬉しくて、もう燃えてきた…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="40" customHeight="1">
+      <c r="A376" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">誰かが見ててくれた…！それだけで、こんなに熱い…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="40" customHeight="1">
+      <c r="A377" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[1]</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreetingGeneric[1]</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてもらえて嬉しいです。頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="40" customHeight="1">
+      <c r="A378" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[2]</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreetingGeneric[2]</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">期待に応えられるよう、全力でやります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="40" customHeight="1">
+      <c r="A379" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreetingGeneric[3]</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreetingGeneric[3]</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここで腕を磨かせてもらいます。よろしくお願いします！</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="40" customHeight="1">
+      <c r="A380" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">所属が決まるって、やっぱり落ち着くね</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="40" customHeight="1">
+      <c r="A381" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">また声がかかって嬉しいよ。今度は長くいたいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="40" customHeight="1">
+      <c r="A382" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.normal._default[3]</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリーも気楽だったけど、やっぱりリングが一番だね</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="40" customHeight="1">
+      <c r="A383" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリーのままで終わる女じゃないって、証明する</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="40" customHeight="1">
+      <c r="A384" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">払ってくれた分は、全部利子つけて返してやる</t>
+        </is>
+      </c>
+    </row>
+    <row r="385" ht="40" customHeight="1">
+      <c r="A385" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう一度、リングに立てるんですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="40" customHeight="1">
+      <c r="A386" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.quiet._default[2]</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…声がかかって、よかったです</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="40" customHeight="1">
+      <c r="A387" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わ、わたしとまた契約してくれる人がいるなんて…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="40" customHeight="1">
+      <c r="A388" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.shy._default[2]</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">こ、今度こそ…長く居られるように、頑張ります…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="40" customHeight="1">
+      <c r="A389" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリーも気楽だったけどねー。ここらで腰を据えるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="40" customHeight="1">
+      <c r="A390" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声かかんなくてさー。拾ってくれて助かったよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="40" customHeight="1">
+      <c r="A391" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう一度チャンスをもらえた。無駄にしません</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="40" customHeight="1">
+      <c r="A392" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾ってくれた恩は、練習の量でお返しします</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="40" customHeight="1">
+      <c r="A393" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">また契約できた…！この嬉しさ、試合で爆発させる…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="40" customHeight="1">
+      <c r="A394" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.emotional._default[2]</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾ってくれた…！この恩、絶対に返す…！</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="40" customHeight="1">
+      <c r="A395" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[1]</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreetingGeneric[1]</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう一度リングに立てます。無駄にしません！</t>
+        </is>
+      </c>
+    </row>
+    <row r="396" ht="40" customHeight="1">
+      <c r="A396" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[2]</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreetingGeneric[2]</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">拾っていただいた恩、必ず返します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="40" customHeight="1">
+      <c r="A397" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreetingGeneric[3]</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreetingGeneric[3]</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">所属を失っていました。ここで、やり直します！</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="40" customHeight="1">
+      <c r="A398" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わったはずなのに、まだ胃の底が重い</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="40" customHeight="1">
+      <c r="A399" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう一度勝てば消えるのかな。……多分、消えない</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="40" customHeight="1">
+      <c r="A400" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った側が、いつまで覚えてなきゃいけないの</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="40" customHeight="1">
+      <c r="A401" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わらせたのは私。付き合ってやるのは、これで最後</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="40" customHeight="1">
+      <c r="A402" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（終わったはずの相手を、じっと見ている）</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="40" customHeight="1">
+      <c r="A403" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…もう終わったのに…どうして、また気になるんだろう…</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="40" customHeight="1">
+      <c r="A404" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">はぁ……また？ もう終わった話でしょ、これ</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="40" customHeight="1">
+      <c r="A405" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝っても軽くならないもんだね。……不思議</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="40" customHeight="1">
+      <c r="A406" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">決着はつきました。……私の中だけ、まだです</t>
+        </is>
+      </c>
+    </row>
+    <row r="407" ht="40" customHeight="1">
+      <c r="A407" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝った人間が引きずるのは、変な話ですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="40" customHeight="1">
+      <c r="A408" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.ahead.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わったって言っただろ……！ なんでまだ、いるんだ</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="40" customHeight="1">
+      <c r="A409" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.normal._default[1]</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わったことにされた。私だけ、置いていかれたまま</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="40" customHeight="1">
+      <c r="A410" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.normal._default[2]</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr" s="5">
+        <is>
+          <t xml:space="preserve">ノーマル</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">忘れられたら楽だったのに。……よく覚えてるんだ、これが</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="40" customHeight="1">
+      <c r="A411" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.bold._default[1]</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わりってことにされてる。でも私はまだ認めない</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="40" customHeight="1">
+      <c r="A412" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.bold._default[2]</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve">強気</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">もう格付けは済んでいるのかも。それでも・・・</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="40" customHeight="1">
+      <c r="A413" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.quiet._default[1]</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr" s="7">
+        <is>
+          <t xml:space="preserve">寡黙</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">………（あの日の敗北の瞬間が、まだ耳から抜けない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="40" customHeight="1">
+      <c r="A414" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.shy._default[1]</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr" s="8">
+        <is>
+          <t xml:space="preserve">内気</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…あの日敗北した屈辱を…まだ、毎晩思い出すんです…</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="40" customHeight="1">
+      <c r="A415" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.easygoing._default[1]</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんな綺麗に忘れてるね。……あたしは忘れないけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="40" customHeight="1">
+      <c r="A416" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.easygoing._default[2]</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr" s="9">
+        <is>
+          <t xml:space="preserve">お気楽</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いつまでやるんだろうね、これ。……やめられないけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="40" customHeight="1">
+      <c r="A417" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.earnest._default[1]</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あの負けを、まだ一度も納得できていません</t>
+        </is>
+      </c>
+    </row>
+    <row r="418" ht="40" customHeight="1">
+      <c r="A418" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.earnest._default[2]</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">真面目</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わったと言われるたび、足元が抜けるんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="40" customHeight="1">
+      <c r="A419" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bitterPrematch.behind.emotional._default[1]</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr" s="10">
+        <is>
+          <t xml:space="preserve">感情的</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">終わってない……！ 勝手に終わらせるな……！</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I319"/>
+  <autoFilter ref="A1:I419"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/その他セリフ/12-選手経歴イベント.xlsx
+++ b/セリフ編集/その他セリフ/12-選手経歴イベント.xlsx
@@ -256,7 +256,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -271,7 +271,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="5">
@@ -288,7 +288,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -303,7 +303,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="5">
@@ -320,7 +320,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -335,7 +335,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
+          <t xml:space="preserve">_default.normal[3]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="5">
@@ -352,7 +352,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -367,7 +367,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="6">
@@ -384,7 +384,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -399,7 +399,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="6">
@@ -416,7 +416,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.bold._default[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.bold[3]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -431,7 +431,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[3]</t>
+          <t xml:space="preserve">_default.bold[3]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="6">
@@ -448,7 +448,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -463,7 +463,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="7">
@@ -480,7 +480,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -495,7 +495,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="7">
@@ -512,7 +512,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.quiet._default[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.quiet[3]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -527,7 +527,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[3]</t>
+          <t xml:space="preserve">_default.quiet[3]</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="7">
@@ -544,7 +544,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -559,7 +559,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="10">
@@ -576,7 +576,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -591,7 +591,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="10">
@@ -608,7 +608,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.earnest._default[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.earnest[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -623,7 +623,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[3]</t>
+          <t xml:space="preserve">_default.earnest[3]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="10">
@@ -640,7 +640,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -655,7 +655,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="10">
@@ -672,7 +672,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -687,7 +687,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="10">
@@ -704,7 +704,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.emotional._default[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.emotional[3]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -719,7 +719,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[3]</t>
+          <t xml:space="preserve">_default.emotional[3]</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="10">
@@ -736,7 +736,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -751,7 +751,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="9">
@@ -768,7 +768,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -783,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="9">
@@ -800,7 +800,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing._default[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -815,7 +815,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[3]</t>
+          <t xml:space="preserve">_default.easygoing[3]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="9">
@@ -832,7 +832,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -847,7 +847,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="8">
@@ -864,7 +864,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.shy._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -879,7 +879,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[2]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="8">
@@ -896,7 +896,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.shy._default[3]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES._default.shy[3]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -911,7 +911,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[3]</t>
+          <t xml:space="preserve">_default.shy[3]</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="8">
@@ -928,7 +928,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -943,7 +943,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F23" t="inlineStr" s="5">
@@ -960,7 +960,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -975,7 +975,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F24" t="inlineStr" s="5">
@@ -992,7 +992,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr" s="6">
@@ -1024,7 +1024,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F26" t="inlineStr" s="6">
@@ -1056,7 +1056,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F27" t="inlineStr" s="7">
@@ -1088,7 +1088,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F28" t="inlineStr" s="8">
@@ -1120,7 +1120,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F29" t="inlineStr" s="9">
@@ -1152,7 +1152,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F30" t="inlineStr" s="9">
@@ -1184,7 +1184,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr" s="10">
@@ -1216,7 +1216,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F32" t="inlineStr" s="10">
@@ -1248,7 +1248,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F33" t="inlineStr" s="10">
@@ -1280,7 +1280,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F34" t="inlineStr" s="5">
@@ -1312,7 +1312,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F35" t="inlineStr" s="5">
@@ -1344,7 +1344,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
+          <t xml:space="preserve">_default.normal[3]</t>
         </is>
       </c>
       <c r="F36" t="inlineStr" s="5">
@@ -1376,7 +1376,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F37" t="inlineStr" s="6">
@@ -1408,7 +1408,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F38" t="inlineStr" s="6">
@@ -1440,7 +1440,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.bold._default[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.bold[3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[3]</t>
+          <t xml:space="preserve">_default.bold[3]</t>
         </is>
       </c>
       <c r="F39" t="inlineStr" s="6">
@@ -1472,7 +1472,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.quiet._default[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.quiet[2]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[2]</t>
+          <t xml:space="preserve">_default.quiet[2]</t>
         </is>
       </c>
       <c r="F40" t="inlineStr" s="7">
@@ -1504,7 +1504,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.quiet._default[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.quiet[3]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[3]</t>
+          <t xml:space="preserve">_default.quiet[3]</t>
         </is>
       </c>
       <c r="F41" t="inlineStr" s="7">
@@ -1536,7 +1536,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F42" t="inlineStr" s="10">
@@ -1568,7 +1568,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F43" t="inlineStr" s="10">
@@ -1600,7 +1600,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.earnest._default[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.earnest[3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[3]</t>
+          <t xml:space="preserve">_default.earnest[3]</t>
         </is>
       </c>
       <c r="F44" t="inlineStr" s="10">
@@ -1632,7 +1632,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F45" t="inlineStr" s="10">
@@ -1664,7 +1664,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F46" t="inlineStr" s="10">
@@ -1696,7 +1696,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.emotional._default[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.emotional[3]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[3]</t>
+          <t xml:space="preserve">_default.emotional[3]</t>
         </is>
       </c>
       <c r="F47" t="inlineStr" s="10">
@@ -1728,7 +1728,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F48" t="inlineStr" s="9">
@@ -1760,7 +1760,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F49" t="inlineStr" s="9">
@@ -1792,7 +1792,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing._default[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[3]</t>
+          <t xml:space="preserve">_default.easygoing[3]</t>
         </is>
       </c>
       <c r="F50" t="inlineStr" s="9">
@@ -1824,7 +1824,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F51" t="inlineStr" s="8">
@@ -1856,7 +1856,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.shy._default[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[2]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
         </is>
       </c>
       <c r="F52" t="inlineStr" s="8">
@@ -1888,7 +1888,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.shy._default[3]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES._default.shy[3]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[3]</t>
+          <t xml:space="preserve">_default.shy[3]</t>
         </is>
       </c>
       <c r="F53" t="inlineStr" s="8">
@@ -1920,7 +1920,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F54" t="inlineStr" s="5">
@@ -1952,7 +1952,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F55" t="inlineStr" s="5">
@@ -1984,7 +1984,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
+          <t xml:space="preserve">_default.normal[3]</t>
         </is>
       </c>
       <c r="F56" t="inlineStr" s="5">
@@ -2016,7 +2016,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F57" t="inlineStr" s="6">
@@ -2048,7 +2048,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F58" t="inlineStr" s="6">
@@ -2080,7 +2080,7 @@
     <row r="59" ht="40" customHeight="1">
       <c r="A59" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="D59" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F59" t="inlineStr" s="7">
@@ -2112,7 +2112,7 @@
     <row r="60" ht="40" customHeight="1">
       <c r="A60" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
@@ -2127,7 +2127,7 @@
       </c>
       <c r="D60" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F60" t="inlineStr" s="8">
@@ -2144,7 +2144,7 @@
     <row r="61" ht="40" customHeight="1">
       <c r="A61" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="D61" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F61" t="inlineStr" s="9">
@@ -2176,7 +2176,7 @@
     <row r="62" ht="40" customHeight="1">
       <c r="A62" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D62" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F62" t="inlineStr" s="9">
@@ -2208,7 +2208,7 @@
     <row r="63" ht="40" customHeight="1">
       <c r="A63" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="D63" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F63" t="inlineStr" s="10">
@@ -2240,7 +2240,7 @@
     <row r="64" ht="40" customHeight="1">
       <c r="A64" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="D64" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F64" t="inlineStr" s="10">
@@ -2272,7 +2272,7 @@
     <row r="65" ht="40" customHeight="1">
       <c r="A65" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="D65" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F65" t="inlineStr" s="10">
@@ -2304,7 +2304,7 @@
     <row r="66" ht="40" customHeight="1">
       <c r="A66" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="D66" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F66" t="inlineStr" s="5">
@@ -2336,7 +2336,7 @@
     <row r="67" ht="40" customHeight="1">
       <c r="A67" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="D67" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F67" t="inlineStr" s="5">
@@ -2368,7 +2368,7 @@
     <row r="68" ht="40" customHeight="1">
       <c r="A68" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="D68" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F68" t="inlineStr" s="6">
@@ -2400,7 +2400,7 @@
     <row r="69" ht="40" customHeight="1">
       <c r="A69" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr" s="2">
@@ -2415,7 +2415,7 @@
       </c>
       <c r="D69" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F69" t="inlineStr" s="6">
@@ -2432,7 +2432,7 @@
     <row r="70" ht="40" customHeight="1">
       <c r="A70" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr" s="2">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="D70" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F70" t="inlineStr" s="7">
@@ -2464,7 +2464,7 @@
     <row r="71" ht="40" customHeight="1">
       <c r="A71" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="D71" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F71" t="inlineStr" s="8">
@@ -2496,7 +2496,7 @@
     <row r="72" ht="40" customHeight="1">
       <c r="A72" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr" s="2">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="D72" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F72" t="inlineStr" s="9">
@@ -2528,7 +2528,7 @@
     <row r="73" ht="40" customHeight="1">
       <c r="A73" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr" s="2">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D73" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F73" t="inlineStr" s="9">
@@ -2560,7 +2560,7 @@
     <row r="74" ht="40" customHeight="1">
       <c r="A74" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr" s="2">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="D74" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F74" t="inlineStr" s="10">
@@ -2592,7 +2592,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr" s="2">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D75" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F75" t="inlineStr" s="10">
@@ -2624,7 +2624,7 @@
     <row r="76" ht="40" customHeight="1">
       <c r="A76" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr" s="2">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="D76" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F76" t="inlineStr" s="10">
@@ -2656,7 +2656,7 @@
     <row r="77" ht="40" customHeight="1">
       <c r="A77" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr" s="2">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D77" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F77" t="inlineStr" s="5">
@@ -2688,7 +2688,7 @@
     <row r="78" ht="40" customHeight="1">
       <c r="A78" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr" s="2">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D78" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F78" t="inlineStr" s="5">
@@ -2720,7 +2720,7 @@
     <row r="79" ht="40" customHeight="1">
       <c r="A79" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr" s="2">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D79" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F79" t="inlineStr" s="6">
@@ -2752,7 +2752,7 @@
     <row r="80" ht="40" customHeight="1">
       <c r="A80" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr" s="2">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="D80" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F80" t="inlineStr" s="6">
@@ -2784,7 +2784,7 @@
     <row r="81" ht="40" customHeight="1">
       <c r="A81" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr" s="2">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D81" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F81" t="inlineStr" s="7">
@@ -2816,7 +2816,7 @@
     <row r="82" ht="40" customHeight="1">
       <c r="A82" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr" s="2">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D82" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F82" t="inlineStr" s="8">
@@ -2848,7 +2848,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F83" t="inlineStr" s="9">
@@ -2880,7 +2880,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F84" t="inlineStr" s="9">
@@ -2912,7 +2912,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F85" t="inlineStr" s="10">
@@ -2944,7 +2944,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F86" t="inlineStr" s="10">
@@ -2976,7 +2976,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F87" t="inlineStr" s="10">
@@ -3008,7 +3008,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3023,7 +3023,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="5">
@@ -3040,7 +3040,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="5">
@@ -3072,7 +3072,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="6">
@@ -3104,7 +3104,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="6">
@@ -3136,7 +3136,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="7">
@@ -3168,7 +3168,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="8">
@@ -3200,7 +3200,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="9">
@@ -3232,7 +3232,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="9">
@@ -3264,7 +3264,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="10">
@@ -3296,7 +3296,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="10">
@@ -3328,7 +3328,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="10">
@@ -3360,7 +3360,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="5">
@@ -3392,7 +3392,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="5">
@@ -3424,7 +3424,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.normal[3]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[3]</t>
+          <t xml:space="preserve">_default.normal[3]</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="5">
@@ -3456,7 +3456,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="6">
@@ -3488,7 +3488,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="6">
@@ -3520,7 +3520,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.bold._default[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.bold[3]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[3]</t>
+          <t xml:space="preserve">_default.bold[3]</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="6">
@@ -3552,7 +3552,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="7">
@@ -3584,7 +3584,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.quiet._default[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.quiet[3]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[3]</t>
+          <t xml:space="preserve">_default.quiet[3]</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="7">
@@ -3616,7 +3616,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="10">
@@ -3648,7 +3648,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="10">
@@ -3680,7 +3680,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.earnest._default[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.earnest[3]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[3]</t>
+          <t xml:space="preserve">_default.earnest[3]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="10">
@@ -3712,7 +3712,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="10">
@@ -3744,7 +3744,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional._default[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.emotional[2]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[2]</t>
+          <t xml:space="preserve">_default.emotional[2]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="10">
@@ -3776,7 +3776,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.emotional._default[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.emotional[3]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[3]</t>
+          <t xml:space="preserve">_default.emotional[3]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="10">
@@ -3808,7 +3808,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="9">
@@ -3840,7 +3840,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="9">
@@ -3872,7 +3872,7 @@
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing._default[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[3]</t>
+          <t xml:space="preserve">_default.easygoing[3]</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="9">
@@ -3904,7 +3904,7 @@
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="8">
@@ -3936,7 +3936,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.shy._default[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.shy[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[2]</t>
+          <t xml:space="preserve">_default.shy[2]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="8">
@@ -3968,7 +3968,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.shy._default[3]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES._default.shy[3]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[3]</t>
+          <t xml:space="preserve">_default.shy[3]</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="8">
@@ -4000,7 +4000,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="5">
@@ -4032,7 +4032,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="5">
@@ -4064,7 +4064,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="6">
@@ -4096,7 +4096,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="6">
@@ -4128,7 +4128,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="7">
@@ -4160,7 +4160,7 @@
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="8">
@@ -4192,7 +4192,7 @@
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="9">
@@ -4224,7 +4224,7 @@
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="9">
@@ -4256,7 +4256,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="10">
@@ -4288,7 +4288,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="10">
@@ -4320,7 +4320,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="10">
@@ -4433,7 +4433,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="5">
@@ -4465,7 +4465,7 @@
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="5">
@@ -4497,7 +4497,7 @@
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="6">
@@ -4529,7 +4529,7 @@
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="6">
@@ -4561,7 +4561,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="7">
@@ -4593,7 +4593,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="8">
@@ -4625,7 +4625,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="9">
@@ -4657,7 +4657,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="9">
@@ -4689,7 +4689,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="10">
@@ -4721,7 +4721,7 @@
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="10">
@@ -4753,7 +4753,7 @@
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="10">
@@ -4866,7 +4866,7 @@
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.normal[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[1]</t>
+          <t xml:space="preserve">_default.normal[1]</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="5">
@@ -4898,7 +4898,7 @@
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.normal[2]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">normal._default[2]</t>
+          <t xml:space="preserve">_default.normal[2]</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="5">
@@ -4930,7 +4930,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.bold[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[1]</t>
+          <t xml:space="preserve">_default.bold[1]</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="6">
@@ -4962,7 +4962,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.bold[2]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bold._default[2]</t>
+          <t xml:space="preserve">_default.bold[2]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="6">
@@ -4994,7 +4994,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.quiet[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">quiet._default[1]</t>
+          <t xml:space="preserve">_default.quiet[1]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="7">
@@ -5026,7 +5026,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.shy[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">shy._default[1]</t>
+          <t xml:space="preserve">_default.shy[1]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="8">
@@ -5058,7 +5058,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[1]</t>
+          <t xml:space="preserve">_default.easygoing[1]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="9">
@@ -5090,7 +5090,7 @@
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing._default[2]</t>
+          <t xml:space="preserve">_default.easygoing[2]</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="9">
@@ -5122,7 +5122,7 @@
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.earnest[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[1]</t>
+          <t xml:space="preserve">_default.earnest[1]</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="10">
@@ -5154,7 +5154,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.earnest[2]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">earnest._default[2]</t>
+          <t xml:space="preserve">_default.earnest[2]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="10">
@@ -5186,7 +5186,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES._default.emotional[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">emotional._default[1]</t>
+          <t xml:space="preserve">_default.emotional[1]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="10">
@@ -5299,7 +5299,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.normal[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal._default[1]</t>
+          <t xml:space="preserve">draftJoin._default.normal[1]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="5">
@@ -5331,7 +5331,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.normal[2]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal._default[2]</t>
+          <t xml:space="preserve">draftJoin._default.normal[2]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="5">
@@ -5363,7 +5363,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.normal[3]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.normal._default[3]</t>
+          <t xml:space="preserve">draftJoin._default.normal[3]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="5">
@@ -5395,7 +5395,7 @@
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.bold[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold._default[1]</t>
+          <t xml:space="preserve">draftJoin._default.bold[1]</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="6">
@@ -5427,7 +5427,7 @@
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.bold[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold._default[2]</t>
+          <t xml:space="preserve">draftJoin._default.bold[2]</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="6">
@@ -5459,7 +5459,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.bold._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.bold[3]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.bold._default[3]</t>
+          <t xml:space="preserve">draftJoin._default.bold[3]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="6">
@@ -5491,7 +5491,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.quiet[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5506,7 +5506,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet._default[1]</t>
+          <t xml:space="preserve">draftJoin._default.quiet[1]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="7">
@@ -5523,7 +5523,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.quiet[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet._default[2]</t>
+          <t xml:space="preserve">draftJoin._default.quiet[2]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="7">
@@ -5555,7 +5555,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.quiet._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.quiet[3]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.quiet._default[3]</t>
+          <t xml:space="preserve">draftJoin._default.quiet[3]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="7">
@@ -5587,7 +5587,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.earnest[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest._default[1]</t>
+          <t xml:space="preserve">draftJoin._default.earnest[1]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="10">
@@ -5619,7 +5619,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.earnest[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest._default[2]</t>
+          <t xml:space="preserve">draftJoin._default.earnest[2]</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="10">
@@ -5651,7 +5651,7 @@
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.earnest._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.earnest[3]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.earnest._default[3]</t>
+          <t xml:space="preserve">draftJoin._default.earnest[3]</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="10">
@@ -5683,7 +5683,7 @@
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.emotional[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.emotional._default[1]</t>
+          <t xml:space="preserve">draftJoin._default.emotional[1]</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="10">
@@ -5715,7 +5715,7 @@
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.emotional[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.emotional._default[2]</t>
+          <t xml:space="preserve">draftJoin._default.emotional[2]</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="10">
@@ -5747,7 +5747,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.emotional._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.emotional[3]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.emotional._default[3]</t>
+          <t xml:space="preserve">draftJoin._default.emotional[3]</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="10">
@@ -5779,7 +5779,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing._default[1]</t>
+          <t xml:space="preserve">draftJoin._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="9">
@@ -5811,7 +5811,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing._default[2]</t>
+          <t xml:space="preserve">draftJoin._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="9">
@@ -5843,7 +5843,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing._default[3]</t>
+          <t xml:space="preserve">draftJoin._default.easygoing[3]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="9">
@@ -5875,7 +5875,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.shy[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.shy._default[1]</t>
+          <t xml:space="preserve">draftJoin._default.shy[1]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="8">
@@ -5907,7 +5907,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.shy._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.shy[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.shy._default[2]</t>
+          <t xml:space="preserve">draftJoin._default.shy[2]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="8">
@@ -5939,7 +5939,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.shy._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin._default.shy[3]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.shy._default[3]</t>
+          <t xml:space="preserve">draftJoin._default.shy[3]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="8">
@@ -5971,7 +5971,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.normal[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal._default[1]</t>
+          <t xml:space="preserve">draftInterest._default.normal[1]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="5">
@@ -6003,7 +6003,7 @@
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.normal[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.normal._default[2]</t>
+          <t xml:space="preserve">draftInterest._default.normal[2]</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="5">
@@ -6035,7 +6035,7 @@
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.bold[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold._default[1]</t>
+          <t xml:space="preserve">draftInterest._default.bold[1]</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="6">
@@ -6067,7 +6067,7 @@
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.bold[2]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.bold._default[2]</t>
+          <t xml:space="preserve">draftInterest._default.bold[2]</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="6">
@@ -6099,7 +6099,7 @@
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.quiet[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.quiet._default[1]</t>
+          <t xml:space="preserve">draftInterest._default.quiet[1]</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="7">
@@ -6131,7 +6131,7 @@
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.shy[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.shy._default[1]</t>
+          <t xml:space="preserve">draftInterest._default.shy[1]</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="8">
@@ -6163,7 +6163,7 @@
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing._default[1]</t>
+          <t xml:space="preserve">draftInterest._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="9">
@@ -6195,7 +6195,7 @@
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing._default[2]</t>
+          <t xml:space="preserve">draftInterest._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="9">
@@ -6227,7 +6227,7 @@
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.earnest[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest._default[1]</t>
+          <t xml:space="preserve">draftInterest._default.earnest[1]</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="10">
@@ -6259,7 +6259,7 @@
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.earnest[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.earnest._default[2]</t>
+          <t xml:space="preserve">draftInterest._default.earnest[2]</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="10">
@@ -6291,7 +6291,7 @@
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest._default.emotional[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.emotional._default[1]</t>
+          <t xml:space="preserve">draftInterest._default.emotional[1]</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="10">
@@ -6323,7 +6323,7 @@
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.normal[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal._default[1]</t>
+          <t xml:space="preserve">injury._default.normal[1]</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="5">
@@ -6355,7 +6355,7 @@
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.normal[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal._default[2]</t>
+          <t xml:space="preserve">injury._default.normal[2]</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="5">
@@ -6387,7 +6387,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.normal[3]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.normal._default[3]</t>
+          <t xml:space="preserve">injury._default.normal[3]</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="5">
@@ -6419,7 +6419,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold._default[1]</t>
+          <t xml:space="preserve">injury._default.bold[1]</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="6">
@@ -6451,7 +6451,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.bold[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold._default[2]</t>
+          <t xml:space="preserve">injury._default.bold[2]</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="6">
@@ -6483,7 +6483,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.bold._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.bold[3]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.bold._default[3]</t>
+          <t xml:space="preserve">injury._default.bold[3]</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="6">
@@ -6515,7 +6515,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.quiet[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.quiet._default[2]</t>
+          <t xml:space="preserve">injury._default.quiet[2]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="7">
@@ -6547,7 +6547,7 @@
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.quiet._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.quiet[3]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.quiet._default[3]</t>
+          <t xml:space="preserve">injury._default.quiet[3]</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="7">
@@ -6579,7 +6579,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.earnest[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest._default[1]</t>
+          <t xml:space="preserve">injury._default.earnest[1]</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="10">
@@ -6611,7 +6611,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.earnest[2]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest._default[2]</t>
+          <t xml:space="preserve">injury._default.earnest[2]</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="10">
@@ -6643,7 +6643,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.earnest._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.earnest[3]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.earnest._default[3]</t>
+          <t xml:space="preserve">injury._default.earnest[3]</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="10">
@@ -6675,7 +6675,7 @@
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.emotional[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.emotional._default[1]</t>
+          <t xml:space="preserve">injury._default.emotional[1]</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="10">
@@ -6707,7 +6707,7 @@
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.emotional[2]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.emotional._default[2]</t>
+          <t xml:space="preserve">injury._default.emotional[2]</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="10">
@@ -6739,7 +6739,7 @@
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.emotional._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.emotional[3]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.emotional._default[3]</t>
+          <t xml:space="preserve">injury._default.emotional[3]</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="10">
@@ -6771,7 +6771,7 @@
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing._default[1]</t>
+          <t xml:space="preserve">injury._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="9">
@@ -6803,7 +6803,7 @@
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing._default[2]</t>
+          <t xml:space="preserve">injury._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="9">
@@ -6835,7 +6835,7 @@
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing._default[3]</t>
+          <t xml:space="preserve">injury._default.easygoing[3]</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="9">
@@ -6867,7 +6867,7 @@
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.shy[1]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.shy._default[1]</t>
+          <t xml:space="preserve">injury._default.shy[1]</t>
         </is>
       </c>
       <c r="F210" t="inlineStr" s="8">
@@ -6899,7 +6899,7 @@
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.shy._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.shy[2]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.shy._default[2]</t>
+          <t xml:space="preserve">injury._default.shy[2]</t>
         </is>
       </c>
       <c r="F211" t="inlineStr" s="8">
@@ -6931,7 +6931,7 @@
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.shy._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury._default.shy[3]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.shy._default[3]</t>
+          <t xml:space="preserve">injury._default.shy[3]</t>
         </is>
       </c>
       <c r="F212" t="inlineStr" s="8">
@@ -6963,7 +6963,7 @@
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.normal[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal._default[1]</t>
+          <t xml:space="preserve">titleWin._default.normal[1]</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="5">
@@ -6995,7 +6995,7 @@
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.normal[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal._default[2]</t>
+          <t xml:space="preserve">titleWin._default.normal[2]</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="5">
@@ -7027,7 +7027,7 @@
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.normal[3]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.normal._default[3]</t>
+          <t xml:space="preserve">titleWin._default.normal[3]</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="5">
@@ -7059,7 +7059,7 @@
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.bold[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold._default[1]</t>
+          <t xml:space="preserve">titleWin._default.bold[1]</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="6">
@@ -7091,7 +7091,7 @@
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.bold[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.bold._default[2]</t>
+          <t xml:space="preserve">titleWin._default.bold[2]</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="6">
@@ -7123,7 +7123,7 @@
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.quiet[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.quiet._default[1]</t>
+          <t xml:space="preserve">titleWin._default.quiet[1]</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="7">
@@ -7155,7 +7155,7 @@
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.shy[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.shy._default[1]</t>
+          <t xml:space="preserve">titleWin._default.shy[1]</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="8">
@@ -7187,7 +7187,7 @@
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing._default[1]</t>
+          <t xml:space="preserve">titleWin._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="9">
@@ -7219,7 +7219,7 @@
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing._default[2]</t>
+          <t xml:space="preserve">titleWin._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="9">
@@ -7251,7 +7251,7 @@
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.earnest[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest._default[1]</t>
+          <t xml:space="preserve">titleWin._default.earnest[1]</t>
         </is>
       </c>
       <c r="F222" t="inlineStr" s="10">
@@ -7283,7 +7283,7 @@
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.earnest[2]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.earnest._default[2]</t>
+          <t xml:space="preserve">titleWin._default.earnest[2]</t>
         </is>
       </c>
       <c r="F223" t="inlineStr" s="10">
@@ -7315,7 +7315,7 @@
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin._default.emotional[1]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.emotional._default[1]</t>
+          <t xml:space="preserve">titleWin._default.emotional[1]</t>
         </is>
       </c>
       <c r="F224" t="inlineStr" s="10">
@@ -7347,7 +7347,7 @@
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.normal[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal._default[1]</t>
+          <t xml:space="preserve">titleDefense._default.normal[1]</t>
         </is>
       </c>
       <c r="F225" t="inlineStr" s="5">
@@ -7379,7 +7379,7 @@
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.normal[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.normal._default[2]</t>
+          <t xml:space="preserve">titleDefense._default.normal[2]</t>
         </is>
       </c>
       <c r="F226" t="inlineStr" s="5">
@@ -7411,7 +7411,7 @@
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.bold[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold._default[1]</t>
+          <t xml:space="preserve">titleDefense._default.bold[1]</t>
         </is>
       </c>
       <c r="F227" t="inlineStr" s="6">
@@ -7443,7 +7443,7 @@
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.bold[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.bold._default[2]</t>
+          <t xml:space="preserve">titleDefense._default.bold[2]</t>
         </is>
       </c>
       <c r="F228" t="inlineStr" s="6">
@@ -7475,7 +7475,7 @@
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.quiet[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.quiet._default[1]</t>
+          <t xml:space="preserve">titleDefense._default.quiet[1]</t>
         </is>
       </c>
       <c r="F229" t="inlineStr" s="7">
@@ -7507,7 +7507,7 @@
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.shy[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.shy._default[1]</t>
+          <t xml:space="preserve">titleDefense._default.shy[1]</t>
         </is>
       </c>
       <c r="F230" t="inlineStr" s="8">
@@ -7539,7 +7539,7 @@
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing._default[1]</t>
+          <t xml:space="preserve">titleDefense._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F231" t="inlineStr" s="9">
@@ -7571,7 +7571,7 @@
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing._default[2]</t>
+          <t xml:space="preserve">titleDefense._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F232" t="inlineStr" s="9">
@@ -7603,7 +7603,7 @@
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.earnest[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest._default[1]</t>
+          <t xml:space="preserve">titleDefense._default.earnest[1]</t>
         </is>
       </c>
       <c r="F233" t="inlineStr" s="10">
@@ -7635,7 +7635,7 @@
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.earnest[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.earnest._default[2]</t>
+          <t xml:space="preserve">titleDefense._default.earnest[2]</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="10">
@@ -7667,7 +7667,7 @@
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense._default.emotional[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.emotional._default[1]</t>
+          <t xml:space="preserve">titleDefense._default.emotional[1]</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="10">
@@ -7699,7 +7699,7 @@
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.normal[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal._default[1]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.normal[1]</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="5">
@@ -7731,7 +7731,7 @@
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.normal[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.normal._default[2]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.normal[2]</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="5">
@@ -7763,7 +7763,7 @@
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.bold[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold._default[1]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.bold[1]</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="6">
@@ -7795,7 +7795,7 @@
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.bold[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.bold._default[2]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.bold[2]</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="6">
@@ -7827,7 +7827,7 @@
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.quiet[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.quiet._default[1]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.quiet[1]</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="7">
@@ -7859,7 +7859,7 @@
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.shy[1]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.shy._default[1]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.shy[1]</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="8">
@@ -7891,7 +7891,7 @@
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing._default[1]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="9">
@@ -7923,7 +7923,7 @@
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing._default[2]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F243" t="inlineStr" s="9">
@@ -7955,7 +7955,7 @@
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.earnest[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest._default[1]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.earnest[1]</t>
         </is>
       </c>
       <c r="F244" t="inlineStr" s="10">
@@ -7987,7 +7987,7 @@
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.earnest[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.earnest._default[2]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.earnest[2]</t>
         </is>
       </c>
       <c r="F245" t="inlineStr" s="10">
@@ -8019,7 +8019,7 @@
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss._default.emotional[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.emotional._default[1]</t>
+          <t xml:space="preserve">titleChallengeLoss._default.emotional[1]</t>
         </is>
       </c>
       <c r="F246" t="inlineStr" s="10">
@@ -8051,7 +8051,7 @@
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.normal[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal._default[1]</t>
+          <t xml:space="preserve">titleLoss._default.normal[1]</t>
         </is>
       </c>
       <c r="F247" t="inlineStr" s="5">
@@ -8083,7 +8083,7 @@
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.normal[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.normal._default[2]</t>
+          <t xml:space="preserve">titleLoss._default.normal[2]</t>
         </is>
       </c>
       <c r="F248" t="inlineStr" s="5">
@@ -8115,7 +8115,7 @@
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.bold[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold._default[1]</t>
+          <t xml:space="preserve">titleLoss._default.bold[1]</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="6">
@@ -8147,7 +8147,7 @@
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.bold[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.bold._default[2]</t>
+          <t xml:space="preserve">titleLoss._default.bold[2]</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="6">
@@ -8179,7 +8179,7 @@
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.quiet[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.quiet._default[1]</t>
+          <t xml:space="preserve">titleLoss._default.quiet[1]</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="7">
@@ -8211,7 +8211,7 @@
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.shy[1]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.shy._default[1]</t>
+          <t xml:space="preserve">titleLoss._default.shy[1]</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="8">
@@ -8243,7 +8243,7 @@
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing._default[1]</t>
+          <t xml:space="preserve">titleLoss._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F253" t="inlineStr" s="9">
@@ -8275,7 +8275,7 @@
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -8290,7 +8290,7 @@
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing._default[2]</t>
+          <t xml:space="preserve">titleLoss._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F254" t="inlineStr" s="9">
@@ -8307,7 +8307,7 @@
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.earnest[1]</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest._default[1]</t>
+          <t xml:space="preserve">titleLoss._default.earnest[1]</t>
         </is>
       </c>
       <c r="F255" t="inlineStr" s="10">
@@ -8339,7 +8339,7 @@
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.earnest[2]</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.earnest._default[2]</t>
+          <t xml:space="preserve">titleLoss._default.earnest[2]</t>
         </is>
       </c>
       <c r="F256" t="inlineStr" s="10">
@@ -8371,7 +8371,7 @@
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss._default.emotional[1]</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -8386,7 +8386,7 @@
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.emotional._default[1]</t>
+          <t xml:space="preserve">titleLoss._default.emotional[1]</t>
         </is>
       </c>
       <c r="F257" t="inlineStr" s="10">
@@ -8403,7 +8403,7 @@
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.normal[1]</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal._default[1]</t>
+          <t xml:space="preserve">release._default.normal[1]</t>
         </is>
       </c>
       <c r="F258" t="inlineStr" s="5">
@@ -8435,7 +8435,7 @@
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.normal[2]</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal._default[2]</t>
+          <t xml:space="preserve">release._default.normal[2]</t>
         </is>
       </c>
       <c r="F259" t="inlineStr" s="5">
@@ -8467,7 +8467,7 @@
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.normal[3]</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.normal._default[3]</t>
+          <t xml:space="preserve">release._default.normal[3]</t>
         </is>
       </c>
       <c r="F260" t="inlineStr" s="5">
@@ -8499,7 +8499,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.bold[1]</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold._default[1]</t>
+          <t xml:space="preserve">release._default.bold[1]</t>
         </is>
       </c>
       <c r="F261" t="inlineStr" s="6">
@@ -8531,7 +8531,7 @@
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.bold[2]</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold._default[2]</t>
+          <t xml:space="preserve">release._default.bold[2]</t>
         </is>
       </c>
       <c r="F262" t="inlineStr" s="6">
@@ -8563,7 +8563,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.bold._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.bold[3]</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.bold._default[3]</t>
+          <t xml:space="preserve">release._default.bold[3]</t>
         </is>
       </c>
       <c r="F263" t="inlineStr" s="6">
@@ -8595,7 +8595,7 @@
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.quiet[1]</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet._default[1]</t>
+          <t xml:space="preserve">release._default.quiet[1]</t>
         </is>
       </c>
       <c r="F264" t="inlineStr" s="7">
@@ -8627,7 +8627,7 @@
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.quiet._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.quiet[3]</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -8642,7 +8642,7 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.quiet._default[3]</t>
+          <t xml:space="preserve">release._default.quiet[3]</t>
         </is>
       </c>
       <c r="F265" t="inlineStr" s="7">
@@ -8659,7 +8659,7 @@
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.earnest[1]</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest._default[1]</t>
+          <t xml:space="preserve">release._default.earnest[1]</t>
         </is>
       </c>
       <c r="F266" t="inlineStr" s="10">
@@ -8691,7 +8691,7 @@
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.earnest[2]</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest._default[2]</t>
+          <t xml:space="preserve">release._default.earnest[2]</t>
         </is>
       </c>
       <c r="F267" t="inlineStr" s="10">
@@ -8723,7 +8723,7 @@
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.earnest._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.earnest[3]</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.earnest._default[3]</t>
+          <t xml:space="preserve">release._default.earnest[3]</t>
         </is>
       </c>
       <c r="F268" t="inlineStr" s="10">
@@ -8755,7 +8755,7 @@
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.emotional[1]</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.emotional._default[1]</t>
+          <t xml:space="preserve">release._default.emotional[1]</t>
         </is>
       </c>
       <c r="F269" t="inlineStr" s="10">
@@ -8787,7 +8787,7 @@
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.emotional[2]</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.emotional._default[2]</t>
+          <t xml:space="preserve">release._default.emotional[2]</t>
         </is>
       </c>
       <c r="F270" t="inlineStr" s="10">
@@ -8819,7 +8819,7 @@
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.emotional._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.emotional[3]</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.emotional._default[3]</t>
+          <t xml:space="preserve">release._default.emotional[3]</t>
         </is>
       </c>
       <c r="F271" t="inlineStr" s="10">
@@ -8851,7 +8851,7 @@
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing._default[1]</t>
+          <t xml:space="preserve">release._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F272" t="inlineStr" s="9">
@@ -8883,7 +8883,7 @@
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing._default[2]</t>
+          <t xml:space="preserve">release._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F273" t="inlineStr" s="9">
@@ -8915,7 +8915,7 @@
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.easygoing[3]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing._default[3]</t>
+          <t xml:space="preserve">release._default.easygoing[3]</t>
         </is>
       </c>
       <c r="F274" t="inlineStr" s="9">
@@ -8947,7 +8947,7 @@
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.shy[1]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.shy._default[1]</t>
+          <t xml:space="preserve">release._default.shy[1]</t>
         </is>
       </c>
       <c r="F275" t="inlineStr" s="8">
@@ -8979,7 +8979,7 @@
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.shy._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.shy[2]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.shy._default[2]</t>
+          <t xml:space="preserve">release._default.shy[2]</t>
         </is>
       </c>
       <c r="F276" t="inlineStr" s="8">
@@ -9011,7 +9011,7 @@
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.shy._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release._default.shy[3]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.shy._default[3]</t>
+          <t xml:space="preserve">release._default.shy[3]</t>
         </is>
       </c>
       <c r="F277" t="inlineStr" s="8">
@@ -9043,7 +9043,7 @@
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.normal[1]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal._default[1]</t>
+          <t xml:space="preserve">faSigning._default.normal[1]</t>
         </is>
       </c>
       <c r="F278" t="inlineStr" s="5">
@@ -9075,7 +9075,7 @@
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.normal[2]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.normal._default[2]</t>
+          <t xml:space="preserve">faSigning._default.normal[2]</t>
         </is>
       </c>
       <c r="F279" t="inlineStr" s="5">
@@ -9107,7 +9107,7 @@
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.bold[1]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold._default[1]</t>
+          <t xml:space="preserve">faSigning._default.bold[1]</t>
         </is>
       </c>
       <c r="F280" t="inlineStr" s="6">
@@ -9139,7 +9139,7 @@
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.bold[2]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.bold._default[2]</t>
+          <t xml:space="preserve">faSigning._default.bold[2]</t>
         </is>
       </c>
       <c r="F281" t="inlineStr" s="6">
@@ -9171,7 +9171,7 @@
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.quiet[1]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.quiet._default[1]</t>
+          <t xml:space="preserve">faSigning._default.quiet[1]</t>
         </is>
       </c>
       <c r="F282" t="inlineStr" s="7">
@@ -9203,7 +9203,7 @@
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.shy[1]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.shy._default[1]</t>
+          <t xml:space="preserve">faSigning._default.shy[1]</t>
         </is>
       </c>
       <c r="F283" t="inlineStr" s="8">
@@ -9235,7 +9235,7 @@
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing._default[1]</t>
+          <t xml:space="preserve">faSigning._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F284" t="inlineStr" s="9">
@@ -9267,7 +9267,7 @@
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing._default[2]</t>
+          <t xml:space="preserve">faSigning._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F285" t="inlineStr" s="9">
@@ -9299,7 +9299,7 @@
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.earnest[1]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest._default[1]</t>
+          <t xml:space="preserve">faSigning._default.earnest[1]</t>
         </is>
       </c>
       <c r="F286" t="inlineStr" s="10">
@@ -9331,7 +9331,7 @@
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.earnest[2]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.earnest._default[2]</t>
+          <t xml:space="preserve">faSigning._default.earnest[2]</t>
         </is>
       </c>
       <c r="F287" t="inlineStr" s="10">
@@ -9363,7 +9363,7 @@
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning._default.emotional[1]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.emotional._default[1]</t>
+          <t xml:space="preserve">faSigning._default.emotional[1]</t>
         </is>
       </c>
       <c r="F288" t="inlineStr" s="10">
@@ -9476,7 +9476,7 @@
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.normal[1]</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal._default[1]</t>
+          <t xml:space="preserve">faWelcome._default.normal[1]</t>
         </is>
       </c>
       <c r="F292" t="inlineStr" s="5">
@@ -9508,7 +9508,7 @@
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.normal[2]</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.normal._default[2]</t>
+          <t xml:space="preserve">faWelcome._default.normal[2]</t>
         </is>
       </c>
       <c r="F293" t="inlineStr" s="5">
@@ -9540,7 +9540,7 @@
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.bold[1]</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold._default[1]</t>
+          <t xml:space="preserve">faWelcome._default.bold[1]</t>
         </is>
       </c>
       <c r="F294" t="inlineStr" s="6">
@@ -9572,7 +9572,7 @@
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.bold[2]</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.bold._default[2]</t>
+          <t xml:space="preserve">faWelcome._default.bold[2]</t>
         </is>
       </c>
       <c r="F295" t="inlineStr" s="6">
@@ -9604,7 +9604,7 @@
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.quiet[1]</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.quiet._default[1]</t>
+          <t xml:space="preserve">faWelcome._default.quiet[1]</t>
         </is>
       </c>
       <c r="F296" t="inlineStr" s="7">
@@ -9636,7 +9636,7 @@
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.shy[1]</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.shy._default[1]</t>
+          <t xml:space="preserve">faWelcome._default.shy[1]</t>
         </is>
       </c>
       <c r="F297" t="inlineStr" s="8">
@@ -9668,7 +9668,7 @@
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing._default[1]</t>
+          <t xml:space="preserve">faWelcome._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F298" t="inlineStr" s="9">
@@ -9700,7 +9700,7 @@
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing._default[2]</t>
+          <t xml:space="preserve">faWelcome._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F299" t="inlineStr" s="9">
@@ -9732,7 +9732,7 @@
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.earnest[1]</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest._default[1]</t>
+          <t xml:space="preserve">faWelcome._default.earnest[1]</t>
         </is>
       </c>
       <c r="F300" t="inlineStr" s="10">
@@ -9764,7 +9764,7 @@
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.earnest[2]</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.earnest._default[2]</t>
+          <t xml:space="preserve">faWelcome._default.earnest[2]</t>
         </is>
       </c>
       <c r="F301" t="inlineStr" s="10">
@@ -9796,7 +9796,7 @@
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome._default.emotional[1]</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.emotional._default[1]</t>
+          <t xml:space="preserve">faWelcome._default.emotional[1]</t>
         </is>
       </c>
       <c r="F302" t="inlineStr" s="10">
@@ -9909,7 +9909,7 @@
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.normal[1]</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal._default[1]</t>
+          <t xml:space="preserve">rentalGreeting._default.normal[1]</t>
         </is>
       </c>
       <c r="F306" t="inlineStr" s="5">
@@ -9941,7 +9941,7 @@
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.normal[2]</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.normal._default[2]</t>
+          <t xml:space="preserve">rentalGreeting._default.normal[2]</t>
         </is>
       </c>
       <c r="F307" t="inlineStr" s="5">
@@ -9973,7 +9973,7 @@
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.bold[1]</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold._default[1]</t>
+          <t xml:space="preserve">rentalGreeting._default.bold[1]</t>
         </is>
       </c>
       <c r="F308" t="inlineStr" s="6">
@@ -10005,7 +10005,7 @@
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.bold[2]</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.bold._default[2]</t>
+          <t xml:space="preserve">rentalGreeting._default.bold[2]</t>
         </is>
       </c>
       <c r="F309" t="inlineStr" s="6">
@@ -10037,7 +10037,7 @@
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.quiet[1]</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.quiet._default[1]</t>
+          <t xml:space="preserve">rentalGreeting._default.quiet[1]</t>
         </is>
       </c>
       <c r="F310" t="inlineStr" s="7">
@@ -10069,7 +10069,7 @@
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.shy[1]</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.shy._default[1]</t>
+          <t xml:space="preserve">rentalGreeting._default.shy[1]</t>
         </is>
       </c>
       <c r="F311" t="inlineStr" s="8">
@@ -10101,7 +10101,7 @@
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing._default[1]</t>
+          <t xml:space="preserve">rentalGreeting._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F312" t="inlineStr" s="9">
@@ -10133,7 +10133,7 @@
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing._default[2]</t>
+          <t xml:space="preserve">rentalGreeting._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F313" t="inlineStr" s="9">
@@ -10165,7 +10165,7 @@
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.earnest[1]</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -10180,7 +10180,7 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest._default[1]</t>
+          <t xml:space="preserve">rentalGreeting._default.earnest[1]</t>
         </is>
       </c>
       <c r="F314" t="inlineStr" s="10">
@@ -10197,7 +10197,7 @@
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.earnest[2]</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.earnest._default[2]</t>
+          <t xml:space="preserve">rentalGreeting._default.earnest[2]</t>
         </is>
       </c>
       <c r="F315" t="inlineStr" s="10">
@@ -10229,7 +10229,7 @@
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting._default.emotional[1]</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.emotional._default[1]</t>
+          <t xml:space="preserve">rentalGreeting._default.emotional[1]</t>
         </is>
       </c>
       <c r="F316" t="inlineStr" s="10">
@@ -10342,7 +10342,7 @@
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh._default.normal[1]</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.normal._default[1]</t>
+          <t xml:space="preserve">heatSelf.fresh._default.normal[1]</t>
         </is>
       </c>
       <c r="F320" t="inlineStr" s="5">
@@ -10374,7 +10374,7 @@
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh._default.bold[1]</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.bold._default[1]</t>
+          <t xml:space="preserve">heatSelf.fresh._default.bold[1]</t>
         </is>
       </c>
       <c r="F321" t="inlineStr" s="6">
@@ -10406,7 +10406,7 @@
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.easygoing._default[1]</t>
+          <t xml:space="preserve">heatSelf.fresh._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F322" t="inlineStr" s="9">
@@ -10438,7 +10438,7 @@
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh._default.earnest[1]</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -10453,7 +10453,7 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.earnest._default[1]</t>
+          <t xml:space="preserve">heatSelf.fresh._default.earnest[1]</t>
         </is>
       </c>
       <c r="F323" t="inlineStr" s="10">
@@ -10470,7 +10470,7 @@
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh._default.emotional[1]</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.emotional._default[1]</t>
+          <t xml:space="preserve">heatSelf.fresh._default.emotional[1]</t>
         </is>
       </c>
       <c r="F324" t="inlineStr" s="10">
@@ -10502,7 +10502,7 @@
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh._default.quiet[1]</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.quiet._default[1]</t>
+          <t xml:space="preserve">heatSelf.fresh._default.quiet[1]</t>
         </is>
       </c>
       <c r="F325" t="inlineStr" s="7">
@@ -10534,7 +10534,7 @@
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.fresh._default.shy[1]</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.fresh.shy._default[1]</t>
+          <t xml:space="preserve">heatSelf.fresh._default.shy[1]</t>
         </is>
       </c>
       <c r="F326" t="inlineStr" s="8">
@@ -10566,7 +10566,7 @@
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm._default.normal[1]</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.normal._default[1]</t>
+          <t xml:space="preserve">heatSelf.warm._default.normal[1]</t>
         </is>
       </c>
       <c r="F327" t="inlineStr" s="5">
@@ -10598,7 +10598,7 @@
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm._default.bold[1]</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.bold._default[1]</t>
+          <t xml:space="preserve">heatSelf.warm._default.bold[1]</t>
         </is>
       </c>
       <c r="F328" t="inlineStr" s="6">
@@ -10630,7 +10630,7 @@
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.easygoing._default[1]</t>
+          <t xml:space="preserve">heatSelf.warm._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F329" t="inlineStr" s="9">
@@ -10662,7 +10662,7 @@
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm._default.earnest[1]</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.earnest._default[1]</t>
+          <t xml:space="preserve">heatSelf.warm._default.earnest[1]</t>
         </is>
       </c>
       <c r="F330" t="inlineStr" s="10">
@@ -10694,7 +10694,7 @@
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm._default.emotional[1]</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -10709,7 +10709,7 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.emotional._default[1]</t>
+          <t xml:space="preserve">heatSelf.warm._default.emotional[1]</t>
         </is>
       </c>
       <c r="F331" t="inlineStr" s="10">
@@ -10726,7 +10726,7 @@
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm._default.quiet[1]</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.quiet._default[1]</t>
+          <t xml:space="preserve">heatSelf.warm._default.quiet[1]</t>
         </is>
       </c>
       <c r="F332" t="inlineStr" s="7">
@@ -10758,7 +10758,7 @@
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.warm._default.shy[1]</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.warm.shy._default[1]</t>
+          <t xml:space="preserve">heatSelf.warm._default.shy[1]</t>
         </is>
       </c>
       <c r="F333" t="inlineStr" s="8">
@@ -10790,7 +10790,7 @@
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy._default.normal[1]</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.normal._default[1]</t>
+          <t xml:space="preserve">heatSelf.heavy._default.normal[1]</t>
         </is>
       </c>
       <c r="F334" t="inlineStr" s="5">
@@ -10822,7 +10822,7 @@
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy._default.bold[1]</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.bold._default[1]</t>
+          <t xml:space="preserve">heatSelf.heavy._default.bold[1]</t>
         </is>
       </c>
       <c r="F335" t="inlineStr" s="6">
@@ -10854,7 +10854,7 @@
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -10869,7 +10869,7 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.easygoing._default[1]</t>
+          <t xml:space="preserve">heatSelf.heavy._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F336" t="inlineStr" s="9">
@@ -10886,7 +10886,7 @@
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy._default.earnest[1]</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.earnest._default[1]</t>
+          <t xml:space="preserve">heatSelf.heavy._default.earnest[1]</t>
         </is>
       </c>
       <c r="F337" t="inlineStr" s="10">
@@ -10918,7 +10918,7 @@
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy._default.emotional[1]</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.emotional._default[1]</t>
+          <t xml:space="preserve">heatSelf.heavy._default.emotional[1]</t>
         </is>
       </c>
       <c r="F338" t="inlineStr" s="10">
@@ -10950,7 +10950,7 @@
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy._default.quiet[1]</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.quiet._default[1]</t>
+          <t xml:space="preserve">heatSelf.heavy._default.quiet[1]</t>
         </is>
       </c>
       <c r="F339" t="inlineStr" s="7">
@@ -10982,7 +10982,7 @@
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.heatSelf.heavy._default.shy[1]</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">heatSelf.heavy.shy._default[1]</t>
+          <t xml:space="preserve">heatSelf.heavy._default.shy[1]</t>
         </is>
       </c>
       <c r="F340" t="inlineStr" s="8">
@@ -11581,7 +11581,7 @@
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.normal[1]</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal._default[1]</t>
+          <t xml:space="preserve">scoutGreeting._default.normal[1]</t>
         </is>
       </c>
       <c r="F362" t="inlineStr" s="5">
@@ -11613,7 +11613,7 @@
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.normal[2]</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal._default[2]</t>
+          <t xml:space="preserve">scoutGreeting._default.normal[2]</t>
         </is>
       </c>
       <c r="F363" t="inlineStr" s="5">
@@ -11645,7 +11645,7 @@
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.normal[3]</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.normal._default[3]</t>
+          <t xml:space="preserve">scoutGreeting._default.normal[3]</t>
         </is>
       </c>
       <c r="F364" t="inlineStr" s="5">
@@ -11677,7 +11677,7 @@
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.bold[1]</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.bold._default[1]</t>
+          <t xml:space="preserve">scoutGreeting._default.bold[1]</t>
         </is>
       </c>
       <c r="F365" t="inlineStr" s="6">
@@ -11709,7 +11709,7 @@
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.bold[2]</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.bold._default[2]</t>
+          <t xml:space="preserve">scoutGreeting._default.bold[2]</t>
         </is>
       </c>
       <c r="F366" t="inlineStr" s="6">
@@ -11741,7 +11741,7 @@
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.quiet[1]</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.quiet._default[1]</t>
+          <t xml:space="preserve">scoutGreeting._default.quiet[1]</t>
         </is>
       </c>
       <c r="F367" t="inlineStr" s="7">
@@ -11773,7 +11773,7 @@
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.quiet._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.quiet[2]</t>
         </is>
       </c>
       <c r="B368" t="inlineStr" s="2">
@@ -11788,7 +11788,7 @@
       </c>
       <c r="D368" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.quiet._default[2]</t>
+          <t xml:space="preserve">scoutGreeting._default.quiet[2]</t>
         </is>
       </c>
       <c r="F368" t="inlineStr" s="7">
@@ -11805,7 +11805,7 @@
     <row r="369" ht="40" customHeight="1">
       <c r="A369" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.shy[1]</t>
         </is>
       </c>
       <c r="B369" t="inlineStr" s="2">
@@ -11820,7 +11820,7 @@
       </c>
       <c r="D369" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.shy._default[1]</t>
+          <t xml:space="preserve">scoutGreeting._default.shy[1]</t>
         </is>
       </c>
       <c r="F369" t="inlineStr" s="8">
@@ -11837,7 +11837,7 @@
     <row r="370" ht="40" customHeight="1">
       <c r="A370" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.shy._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.shy[2]</t>
         </is>
       </c>
       <c r="B370" t="inlineStr" s="2">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="D370" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.shy._default[2]</t>
+          <t xml:space="preserve">scoutGreeting._default.shy[2]</t>
         </is>
       </c>
       <c r="F370" t="inlineStr" s="8">
@@ -11869,7 +11869,7 @@
     <row r="371" ht="40" customHeight="1">
       <c r="A371" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B371" t="inlineStr" s="2">
@@ -11884,7 +11884,7 @@
       </c>
       <c r="D371" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.easygoing._default[1]</t>
+          <t xml:space="preserve">scoutGreeting._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F371" t="inlineStr" s="9">
@@ -11901,7 +11901,7 @@
     <row r="372" ht="40" customHeight="1">
       <c r="A372" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B372" t="inlineStr" s="2">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="D372" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.easygoing._default[2]</t>
+          <t xml:space="preserve">scoutGreeting._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F372" t="inlineStr" s="9">
@@ -11933,7 +11933,7 @@
     <row r="373" ht="40" customHeight="1">
       <c r="A373" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.earnest[1]</t>
         </is>
       </c>
       <c r="B373" t="inlineStr" s="2">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="D373" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.earnest._default[1]</t>
+          <t xml:space="preserve">scoutGreeting._default.earnest[1]</t>
         </is>
       </c>
       <c r="F373" t="inlineStr" s="10">
@@ -11965,7 +11965,7 @@
     <row r="374" ht="40" customHeight="1">
       <c r="A374" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.earnest[2]</t>
         </is>
       </c>
       <c r="B374" t="inlineStr" s="2">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="D374" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.earnest._default[2]</t>
+          <t xml:space="preserve">scoutGreeting._default.earnest[2]</t>
         </is>
       </c>
       <c r="F374" t="inlineStr" s="10">
@@ -11997,7 +11997,7 @@
     <row r="375" ht="40" customHeight="1">
       <c r="A375" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.emotional[1]</t>
         </is>
       </c>
       <c r="B375" t="inlineStr" s="2">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="D375" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.emotional._default[1]</t>
+          <t xml:space="preserve">scoutGreeting._default.emotional[1]</t>
         </is>
       </c>
       <c r="F375" t="inlineStr" s="10">
@@ -12029,7 +12029,7 @@
     <row r="376" ht="40" customHeight="1">
       <c r="A376" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.emotional._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting._default.emotional[2]</t>
         </is>
       </c>
       <c r="B376" t="inlineStr" s="2">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="D376" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.emotional._default[2]</t>
+          <t xml:space="preserve">scoutGreeting._default.emotional[2]</t>
         </is>
       </c>
       <c r="F376" t="inlineStr" s="10">
@@ -12142,7 +12142,7 @@
     <row r="380" ht="40" customHeight="1">
       <c r="A380" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.normal[1]</t>
         </is>
       </c>
       <c r="B380" t="inlineStr" s="2">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="D380" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal._default[1]</t>
+          <t xml:space="preserve">faGreeting._default.normal[1]</t>
         </is>
       </c>
       <c r="F380" t="inlineStr" s="5">
@@ -12174,7 +12174,7 @@
     <row r="381" ht="40" customHeight="1">
       <c r="A381" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.normal[2]</t>
         </is>
       </c>
       <c r="B381" t="inlineStr" s="2">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="D381" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal._default[2]</t>
+          <t xml:space="preserve">faGreeting._default.normal[2]</t>
         </is>
       </c>
       <c r="F381" t="inlineStr" s="5">
@@ -12206,7 +12206,7 @@
     <row r="382" ht="40" customHeight="1">
       <c r="A382" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.normal._default[3]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.normal[3]</t>
         </is>
       </c>
       <c r="B382" t="inlineStr" s="2">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="D382" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.normal._default[3]</t>
+          <t xml:space="preserve">faGreeting._default.normal[3]</t>
         </is>
       </c>
       <c r="F382" t="inlineStr" s="5">
@@ -12238,7 +12238,7 @@
     <row r="383" ht="40" customHeight="1">
       <c r="A383" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.bold[1]</t>
         </is>
       </c>
       <c r="B383" t="inlineStr" s="2">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="D383" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.bold._default[1]</t>
+          <t xml:space="preserve">faGreeting._default.bold[1]</t>
         </is>
       </c>
       <c r="F383" t="inlineStr" s="6">
@@ -12270,7 +12270,7 @@
     <row r="384" ht="40" customHeight="1">
       <c r="A384" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.bold[2]</t>
         </is>
       </c>
       <c r="B384" t="inlineStr" s="2">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="D384" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.bold._default[2]</t>
+          <t xml:space="preserve">faGreeting._default.bold[2]</t>
         </is>
       </c>
       <c r="F384" t="inlineStr" s="6">
@@ -12302,7 +12302,7 @@
     <row r="385" ht="40" customHeight="1">
       <c r="A385" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.quiet[1]</t>
         </is>
       </c>
       <c r="B385" t="inlineStr" s="2">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="D385" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.quiet._default[1]</t>
+          <t xml:space="preserve">faGreeting._default.quiet[1]</t>
         </is>
       </c>
       <c r="F385" t="inlineStr" s="7">
@@ -12334,7 +12334,7 @@
     <row r="386" ht="40" customHeight="1">
       <c r="A386" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.quiet._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.quiet[2]</t>
         </is>
       </c>
       <c r="B386" t="inlineStr" s="2">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="D386" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.quiet._default[2]</t>
+          <t xml:space="preserve">faGreeting._default.quiet[2]</t>
         </is>
       </c>
       <c r="F386" t="inlineStr" s="7">
@@ -12366,7 +12366,7 @@
     <row r="387" ht="40" customHeight="1">
       <c r="A387" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.shy[1]</t>
         </is>
       </c>
       <c r="B387" t="inlineStr" s="2">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="D387" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.shy._default[1]</t>
+          <t xml:space="preserve">faGreeting._default.shy[1]</t>
         </is>
       </c>
       <c r="F387" t="inlineStr" s="8">
@@ -12398,7 +12398,7 @@
     <row r="388" ht="40" customHeight="1">
       <c r="A388" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.shy._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.shy[2]</t>
         </is>
       </c>
       <c r="B388" t="inlineStr" s="2">
@@ -12413,7 +12413,7 @@
       </c>
       <c r="D388" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.shy._default[2]</t>
+          <t xml:space="preserve">faGreeting._default.shy[2]</t>
         </is>
       </c>
       <c r="F388" t="inlineStr" s="8">
@@ -12430,7 +12430,7 @@
     <row r="389" ht="40" customHeight="1">
       <c r="A389" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B389" t="inlineStr" s="2">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="D389" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.easygoing._default[1]</t>
+          <t xml:space="preserve">faGreeting._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F389" t="inlineStr" s="9">
@@ -12462,7 +12462,7 @@
     <row r="390" ht="40" customHeight="1">
       <c r="A390" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B390" t="inlineStr" s="2">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="D390" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.easygoing._default[2]</t>
+          <t xml:space="preserve">faGreeting._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F390" t="inlineStr" s="9">
@@ -12494,7 +12494,7 @@
     <row r="391" ht="40" customHeight="1">
       <c r="A391" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.earnest[1]</t>
         </is>
       </c>
       <c r="B391" t="inlineStr" s="2">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="D391" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.earnest._default[1]</t>
+          <t xml:space="preserve">faGreeting._default.earnest[1]</t>
         </is>
       </c>
       <c r="F391" t="inlineStr" s="10">
@@ -12526,7 +12526,7 @@
     <row r="392" ht="40" customHeight="1">
       <c r="A392" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.earnest[2]</t>
         </is>
       </c>
       <c r="B392" t="inlineStr" s="2">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="D392" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.earnest._default[2]</t>
+          <t xml:space="preserve">faGreeting._default.earnest[2]</t>
         </is>
       </c>
       <c r="F392" t="inlineStr" s="10">
@@ -12558,7 +12558,7 @@
     <row r="393" ht="40" customHeight="1">
       <c r="A393" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.emotional[1]</t>
         </is>
       </c>
       <c r="B393" t="inlineStr" s="2">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="D393" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.emotional._default[1]</t>
+          <t xml:space="preserve">faGreeting._default.emotional[1]</t>
         </is>
       </c>
       <c r="F393" t="inlineStr" s="10">
@@ -12590,7 +12590,7 @@
     <row r="394" ht="40" customHeight="1">
       <c r="A394" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.emotional._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting._default.emotional[2]</t>
         </is>
       </c>
       <c r="B394" t="inlineStr" s="2">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="D394" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.emotional._default[2]</t>
+          <t xml:space="preserve">faGreeting._default.emotional[2]</t>
         </is>
       </c>
       <c r="F394" t="inlineStr" s="10">
@@ -12703,7 +12703,7 @@
     <row r="398" ht="40" customHeight="1">
       <c r="A398" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.normal[1]</t>
         </is>
       </c>
       <c r="B398" t="inlineStr" s="2">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="D398" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.normal._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.normal[1]</t>
         </is>
       </c>
       <c r="F398" t="inlineStr" s="5">
@@ -12735,7 +12735,7 @@
     <row r="399" ht="40" customHeight="1">
       <c r="A399" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.normal[2]</t>
         </is>
       </c>
       <c r="B399" t="inlineStr" s="2">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="D399" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.normal._default[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.normal[2]</t>
         </is>
       </c>
       <c r="F399" t="inlineStr" s="5">
@@ -12767,7 +12767,7 @@
     <row r="400" ht="40" customHeight="1">
       <c r="A400" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.bold[1]</t>
         </is>
       </c>
       <c r="B400" t="inlineStr" s="2">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="D400" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.bold._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.bold[1]</t>
         </is>
       </c>
       <c r="F400" t="inlineStr" s="6">
@@ -12799,7 +12799,7 @@
     <row r="401" ht="40" customHeight="1">
       <c r="A401" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.bold[2]</t>
         </is>
       </c>
       <c r="B401" t="inlineStr" s="2">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="D401" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.bold._default[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.bold[2]</t>
         </is>
       </c>
       <c r="F401" t="inlineStr" s="6">
@@ -12831,7 +12831,7 @@
     <row r="402" ht="40" customHeight="1">
       <c r="A402" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.quiet[1]</t>
         </is>
       </c>
       <c r="B402" t="inlineStr" s="2">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="D402" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.quiet._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.quiet[1]</t>
         </is>
       </c>
       <c r="F402" t="inlineStr" s="7">
@@ -12863,7 +12863,7 @@
     <row r="403" ht="40" customHeight="1">
       <c r="A403" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.shy[1]</t>
         </is>
       </c>
       <c r="B403" t="inlineStr" s="2">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="D403" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.shy._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.shy[1]</t>
         </is>
       </c>
       <c r="F403" t="inlineStr" s="8">
@@ -12895,7 +12895,7 @@
     <row r="404" ht="40" customHeight="1">
       <c r="A404" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B404" t="inlineStr" s="2">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="D404" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.easygoing._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F404" t="inlineStr" s="9">
@@ -12927,7 +12927,7 @@
     <row r="405" ht="40" customHeight="1">
       <c r="A405" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B405" t="inlineStr" s="2">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="D405" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.easygoing._default[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F405" t="inlineStr" s="9">
@@ -12959,7 +12959,7 @@
     <row r="406" ht="40" customHeight="1">
       <c r="A406" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.earnest[1]</t>
         </is>
       </c>
       <c r="B406" t="inlineStr" s="2">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="D406" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.earnest._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.earnest[1]</t>
         </is>
       </c>
       <c r="F406" t="inlineStr" s="10">
@@ -12991,7 +12991,7 @@
     <row r="407" ht="40" customHeight="1">
       <c r="A407" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.earnest[2]</t>
         </is>
       </c>
       <c r="B407" t="inlineStr" s="2">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="D407" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.earnest._default[2]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.earnest[2]</t>
         </is>
       </c>
       <c r="F407" t="inlineStr" s="10">
@@ -13023,7 +13023,7 @@
     <row r="408" ht="40" customHeight="1">
       <c r="A408" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.ahead._default.emotional[1]</t>
         </is>
       </c>
       <c r="B408" t="inlineStr" s="2">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="D408" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.ahead.emotional._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.ahead._default.emotional[1]</t>
         </is>
       </c>
       <c r="F408" t="inlineStr" s="10">
@@ -13055,7 +13055,7 @@
     <row r="409" ht="40" customHeight="1">
       <c r="A409" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.normal[1]</t>
         </is>
       </c>
       <c r="B409" t="inlineStr" s="2">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="D409" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.normal._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.normal[1]</t>
         </is>
       </c>
       <c r="F409" t="inlineStr" s="5">
@@ -13087,7 +13087,7 @@
     <row r="410" ht="40" customHeight="1">
       <c r="A410" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.normal._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.normal[2]</t>
         </is>
       </c>
       <c r="B410" t="inlineStr" s="2">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="D410" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.normal._default[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.normal[2]</t>
         </is>
       </c>
       <c r="F410" t="inlineStr" s="5">
@@ -13119,7 +13119,7 @@
     <row r="411" ht="40" customHeight="1">
       <c r="A411" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.bold[1]</t>
         </is>
       </c>
       <c r="B411" t="inlineStr" s="2">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="D411" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.bold._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.bold[1]</t>
         </is>
       </c>
       <c r="F411" t="inlineStr" s="6">
@@ -13151,7 +13151,7 @@
     <row r="412" ht="40" customHeight="1">
       <c r="A412" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.bold._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.bold[2]</t>
         </is>
       </c>
       <c r="B412" t="inlineStr" s="2">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="D412" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.bold._default[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.bold[2]</t>
         </is>
       </c>
       <c r="F412" t="inlineStr" s="6">
@@ -13183,7 +13183,7 @@
     <row r="413" ht="40" customHeight="1">
       <c r="A413" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.quiet._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.quiet[1]</t>
         </is>
       </c>
       <c r="B413" t="inlineStr" s="2">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="D413" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.quiet._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.quiet[1]</t>
         </is>
       </c>
       <c r="F413" t="inlineStr" s="7">
@@ -13215,7 +13215,7 @@
     <row r="414" ht="40" customHeight="1">
       <c r="A414" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.shy._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.shy[1]</t>
         </is>
       </c>
       <c r="B414" t="inlineStr" s="2">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="D414" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.shy._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.shy[1]</t>
         </is>
       </c>
       <c r="F414" t="inlineStr" s="8">
@@ -13247,7 +13247,7 @@
     <row r="415" ht="40" customHeight="1">
       <c r="A415" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.easygoing._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.easygoing[1]</t>
         </is>
       </c>
       <c r="B415" t="inlineStr" s="2">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="D415" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.easygoing._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.easygoing[1]</t>
         </is>
       </c>
       <c r="F415" t="inlineStr" s="9">
@@ -13279,7 +13279,7 @@
     <row r="416" ht="40" customHeight="1">
       <c r="A416" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.easygoing._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.easygoing[2]</t>
         </is>
       </c>
       <c r="B416" t="inlineStr" s="2">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="D416" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.easygoing._default[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.easygoing[2]</t>
         </is>
       </c>
       <c r="F416" t="inlineStr" s="9">
@@ -13311,7 +13311,7 @@
     <row r="417" ht="40" customHeight="1">
       <c r="A417" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.earnest[1]</t>
         </is>
       </c>
       <c r="B417" t="inlineStr" s="2">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="D417" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.earnest._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.earnest[1]</t>
         </is>
       </c>
       <c r="F417" t="inlineStr" s="10">
@@ -13343,7 +13343,7 @@
     <row r="418" ht="40" customHeight="1">
       <c r="A418" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.earnest._default[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.earnest[2]</t>
         </is>
       </c>
       <c r="B418" t="inlineStr" s="2">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="D418" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.earnest._default[2]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.earnest[2]</t>
         </is>
       </c>
       <c r="F418" t="inlineStr" s="10">
@@ -13375,7 +13375,7 @@
     <row r="419" ht="40" customHeight="1">
       <c r="A419" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind.emotional._default[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.bitterPrematch.behind._default.emotional[1]</t>
         </is>
       </c>
       <c r="B419" t="inlineStr" s="2">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="D419" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bitterPrematch.behind.emotional._default[1]</t>
+          <t xml:space="preserve">bitterPrematch.behind._default.emotional[1]</t>
         </is>
       </c>
       <c r="F419" t="inlineStr" s="10">
